--- a/MILP/model_output/master_solution_decisions.xlsx
+++ b/MILP/model_output/master_solution_decisions.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="20">
   <si>
     <t>origin</t>
   </si>
@@ -43,7 +43,22 @@
     <t>Aarau</t>
   </si>
   <si>
-    <t>Chiasso</t>
+    <t>Basel</t>
+  </si>
+  <si>
+    <t>Bern</t>
+  </si>
+  <si>
+    <t>Lausanne</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Olten</t>
+  </si>
+  <si>
+    <t>Schaffhausen</t>
   </si>
   <si>
     <t>Stabio</t>
@@ -52,7 +67,7 @@
     <t>Visp</t>
   </si>
   <si>
-    <t>Baselwolf</t>
+    <t>Winterthur</t>
   </si>
   <si>
     <t>Road</t>
@@ -416,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -450,22 +465,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>3.287119813793048</v>
+        <v>16.6512603563023</v>
       </c>
       <c r="F2">
-        <v>255.74848</v>
+        <v>211.1408</v>
       </c>
       <c r="G2">
-        <v>2.939999999999987</v>
+        <v>7</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -476,22 +491,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1.929375</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>249.020128</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>144.06</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>80</v>
@@ -499,25 +514,25 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>112</v>
+        <v>20.03428632743605</v>
       </c>
       <c r="F4">
-        <v>249.65772</v>
+        <v>265.4132</v>
       </c>
       <c r="G4">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -525,13 +540,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -554,22 +569,22 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>0.209999999999976</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>287.2431020479866</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.209999999999976</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -580,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.2598750000000003</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>356.8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>20.79000000000002</v>
       </c>
       <c r="H7">
         <v>80</v>
@@ -603,25 +618,25 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.1399999999999579</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>362.4494294535604</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.139999999999997</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -629,25 +644,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.1732499999999997</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>433.6</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>13.86</v>
       </c>
       <c r="H9">
         <v>80</v>
@@ -658,22 +673,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>63</v>
+        <v>0.859349996480743</v>
       </c>
       <c r="F10">
-        <v>229.86704</v>
+        <v>289.832</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>0.2099999999999937</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -684,22 +699,22 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.259874999999957</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>337.6</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>20.79000000000002</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -707,25 +722,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1.679999999999999</v>
       </c>
       <c r="F12">
-        <v>250.64208</v>
+        <v>238.784</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1.679999999999999</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -733,25 +748,25 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0.2415</v>
       </c>
       <c r="F13">
-        <v>243.304088</v>
+        <v>184</v>
       </c>
       <c r="G13">
-        <v>49</v>
+        <v>19.32</v>
       </c>
       <c r="H13">
         <v>80</v>
@@ -759,13 +774,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -774,7 +789,7 @@
         <v>1764</v>
       </c>
       <c r="F14">
-        <v>334.4031187301584</v>
+        <v>510.6296</v>
       </c>
       <c r="G14">
         <v>1764</v>
@@ -785,13 +800,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -811,25 +826,25 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1442</v>
+        <v>24.86208215122846</v>
       </c>
       <c r="F16">
-        <v>332.5168877669899</v>
+        <v>341.4788</v>
       </c>
       <c r="G16">
-        <v>1442</v>
+        <v>7</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -837,27 +852,1015 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0.1399999999999957</v>
+      </c>
+      <c r="F18">
+        <v>286.8484481991954</v>
+      </c>
+      <c r="G18">
+        <v>0.139999999999997</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0.17325</v>
+      </c>
+      <c r="F19">
+        <v>356.8</v>
+      </c>
+      <c r="G19">
+        <v>13.86</v>
+      </c>
+      <c r="H19">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>25.03523566281445</v>
+      </c>
+      <c r="F20">
+        <v>350.5112</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>24.24278006375409</v>
+      </c>
+      <c r="F22">
+        <v>337.5008</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0.1399999999999957</v>
+      </c>
+      <c r="F24">
+        <v>383.8650001926061</v>
+      </c>
+      <c r="G24">
+        <v>0.139999999999997</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0.17325</v>
+      </c>
+      <c r="F25">
+        <v>456</v>
+      </c>
+      <c r="G25">
+        <v>13.86</v>
+      </c>
+      <c r="H25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0.715383504980014</v>
+      </c>
+      <c r="F26">
+        <v>186.236</v>
+      </c>
+      <c r="G26">
+        <v>0.1399999999999992</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0.1732499999999997</v>
+      </c>
+      <c r="F27">
+        <v>232</v>
+      </c>
+      <c r="G27">
+        <v>13.86000000000002</v>
+      </c>
+      <c r="H27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
         <v>9</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0.1399999999999613</v>
+      </c>
+      <c r="F28">
+        <v>227.1146568560687</v>
+      </c>
+      <c r="G28">
+        <v>0.139999999999981</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0.1732500000000002</v>
+      </c>
+      <c r="F29">
+        <v>297.6</v>
+      </c>
+      <c r="G29">
+        <v>13.86000000000002</v>
+      </c>
+      <c r="H29">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0.5599999999999312</v>
+      </c>
+      <c r="F30">
+        <v>358.4188976461649</v>
+      </c>
+      <c r="G30">
+        <v>0.5599999999999739</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0.6930000000000003</v>
+      </c>
+      <c r="F31">
+        <v>433.6</v>
+      </c>
+      <c r="G31">
+        <v>55.44000000000003</v>
+      </c>
+      <c r="H31">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1442</v>
+      </c>
+      <c r="F32">
+        <v>509.288</v>
+      </c>
+      <c r="G32">
+        <v>1442</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>28.79875416738333</v>
+      </c>
+      <c r="F34">
+        <v>412.5524</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0.1399999999999547</v>
+      </c>
+      <c r="F36">
+        <v>416.3779374891614</v>
+      </c>
+      <c r="G36">
+        <v>0.1399999999999997</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0.1732499999999993</v>
+      </c>
+      <c r="F37">
+        <v>491.2</v>
+      </c>
+      <c r="G37">
+        <v>13.86000000000001</v>
+      </c>
+      <c r="H37">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0.410760945499181</v>
+      </c>
+      <c r="F38">
+        <v>366.884</v>
+      </c>
+      <c r="G38">
+        <v>0.35</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0.4331249999999992</v>
+      </c>
+      <c r="F39">
+        <v>443.2</v>
+      </c>
+      <c r="G39">
+        <v>34.65</v>
+      </c>
+      <c r="H39">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>0.7788180732869956</v>
+      </c>
+      <c r="F40">
+        <v>290.48</v>
+      </c>
+      <c r="G40">
+        <v>0.1399999999999935</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>0.1732499999999777</v>
+      </c>
+      <c r="F41">
+        <v>337.6</v>
+      </c>
+      <c r="G41">
+        <v>13.86000000000001</v>
+      </c>
+      <c r="H41">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1.4701137176229</v>
+      </c>
+      <c r="F42">
+        <v>446.6852000000001</v>
+      </c>
+      <c r="G42">
+        <v>0.21</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>0.259875</v>
+      </c>
+      <c r="F43">
+        <v>379.2</v>
+      </c>
+      <c r="G43">
+        <v>20.79</v>
+      </c>
+      <c r="H43">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>2.172932294851431</v>
+      </c>
+      <c r="F44">
+        <v>353.4128</v>
+      </c>
+      <c r="G44">
+        <v>2.1</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0.14875</v>
+      </c>
+      <c r="F45">
+        <v>228.8</v>
+      </c>
+      <c r="G45">
+        <v>11.9</v>
+      </c>
+      <c r="H45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
         <v>12</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>25.34120000919953</v>
+      </c>
+      <c r="F46">
+        <v>352.82</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0.28</v>
+      </c>
+      <c r="F48">
+        <v>493.3760000000001</v>
+      </c>
+      <c r="G48">
+        <v>0.28</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>0.1715</v>
+      </c>
+      <c r="F49">
+        <v>578.4978303068915</v>
+      </c>
+      <c r="G49">
+        <v>13.72</v>
+      </c>
+      <c r="H49">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1.820000000000002</v>
+      </c>
+      <c r="F50">
+        <v>267.8624</v>
+      </c>
+      <c r="G50">
+        <v>1.820000000000002</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>0.15225</v>
+      </c>
+      <c r="F51">
+        <v>184</v>
+      </c>
+      <c r="G51">
+        <v>12.18</v>
+      </c>
+      <c r="H51">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>2.052104457433294</v>
+      </c>
+      <c r="F52">
+        <v>350.4488000000001</v>
+      </c>
+      <c r="G52">
+        <v>1.75</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>0.415625</v>
+      </c>
+      <c r="F53">
+        <v>249.6</v>
+      </c>
+      <c r="G53">
+        <v>33.25</v>
+      </c>
+      <c r="H53">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1.744667190763831</v>
+      </c>
+      <c r="F54">
+        <v>471.2396000000001</v>
+      </c>
+      <c r="G54">
+        <v>0.5599999999999739</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>0.6929999999999987</v>
+      </c>
+      <c r="F55">
+        <v>443.2</v>
+      </c>
+      <c r="G55">
+        <v>55.44000000000007</v>
+      </c>
+      <c r="H55">
         <v>80</v>
       </c>
     </row>

--- a/MILP/model_output/master_solution_decisions.xlsx
+++ b/MILP/model_output/master_solution_decisions.xlsx
@@ -578,13 +578,13 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>0.209999999999976</v>
+        <v>22.47188389551929</v>
       </c>
       <c r="F6">
-        <v>287.2431020479866</v>
+        <v>308.7967999997442</v>
       </c>
       <c r="G6">
-        <v>0.209999999999976</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -601,16 +601,16 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.2598750000000003</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>356.8</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>20.79000000000002</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>80</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0.1399999999999579</v>
+        <v>27.28394913784358</v>
       </c>
       <c r="F8">
-        <v>362.4494294535604</v>
+        <v>387.764</v>
       </c>
       <c r="G8">
-        <v>0.139999999999997</v>
+        <v>14</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -653,16 +653,16 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.1732499999999997</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>433.6</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>13.86</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>80</v>
@@ -682,13 +682,13 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>0.859349996480743</v>
+        <v>26.82756624371143</v>
       </c>
       <c r="F10">
-        <v>289.832</v>
+        <v>376.7816</v>
       </c>
       <c r="G10">
-        <v>0.2099999999999937</v>
+        <v>21</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -705,16 +705,16 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.259874999999957</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>337.6</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>20.79000000000002</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -734,13 +734,13 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>1.679999999999999</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>238.784</v>
       </c>
       <c r="G12">
-        <v>1.679999999999999</v>
+        <v>21</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -757,16 +757,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.2415</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>80</v>
@@ -890,13 +890,13 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0.1399999999999957</v>
+        <v>23.1341632769456</v>
       </c>
       <c r="F18">
-        <v>286.8484481991954</v>
+        <v>319.2488</v>
       </c>
       <c r="G18">
-        <v>0.139999999999997</v>
+        <v>14</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0.17325</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>356.8</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>13.86</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>80</v>
@@ -1046,13 +1046,13 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>0.1399999999999957</v>
+        <v>29.11803213782482</v>
       </c>
       <c r="F24">
-        <v>383.8650001926061</v>
+        <v>417.5912</v>
       </c>
       <c r="G24">
-        <v>0.139999999999997</v>
+        <v>14</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1069,16 +1069,16 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>0.17325</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>13.86</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>80</v>
@@ -1098,13 +1098,13 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>0.715383504980014</v>
+        <v>18.55750215455832</v>
       </c>
       <c r="F26">
-        <v>186.236</v>
+        <v>242.1068</v>
       </c>
       <c r="G26">
-        <v>0.1399999999999992</v>
+        <v>14</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1121,16 +1121,16 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0.1732499999999997</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>13.86000000000002</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>80</v>
@@ -1150,13 +1150,13 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>0.1399999999999613</v>
+        <v>21.36816696940135</v>
       </c>
       <c r="F28">
-        <v>227.1146568560687</v>
+        <v>289.0472</v>
       </c>
       <c r="G28">
-        <v>0.139999999999981</v>
+        <v>14</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1173,16 +1173,16 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.1732500000000002</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>297.6</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>13.86000000000002</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>80</v>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0.5599999999999312</v>
+        <v>0.559999999999917</v>
       </c>
       <c r="F30">
-        <v>358.4188976461649</v>
+        <v>358.4188976461648</v>
       </c>
       <c r="G30">
         <v>0.5599999999999739</v>
@@ -1228,13 +1228,13 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0.6930000000000003</v>
+        <v>0.6929999999999998</v>
       </c>
       <c r="F31">
         <v>433.6</v>
       </c>
       <c r="G31">
-        <v>55.44000000000003</v>
+        <v>55.44000000000007</v>
       </c>
       <c r="H31">
         <v>80</v>
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>0.1399999999999547</v>
+        <v>33.12053028750031</v>
       </c>
       <c r="F36">
-        <v>416.3779374891614</v>
+        <v>482.1439999999999</v>
       </c>
       <c r="G36">
-        <v>0.1399999999999997</v>
+        <v>14</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1381,16 +1381,16 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>0.1732499999999993</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>491.2</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>13.86000000000001</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>80</v>
@@ -1410,13 +1410,13 @@
         <v>1</v>
       </c>
       <c r="E38">
-        <v>0.410760945499181</v>
+        <v>35</v>
       </c>
       <c r="F38">
-        <v>366.884</v>
+        <v>476.9492</v>
       </c>
       <c r="G38">
-        <v>0.35</v>
+        <v>35</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -1433,16 +1433,16 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.4331249999999992</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>443.2</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>34.65</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>80</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>0.7788180732869956</v>
+        <v>26.88094398490031</v>
       </c>
       <c r="F40">
-        <v>290.48</v>
+        <v>377.624</v>
       </c>
       <c r="G40">
-        <v>0.1399999999999935</v>
+        <v>14</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>19</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0.1732499999999777</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>337.6</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>13.86000000000001</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>80</v>
@@ -1514,13 +1514,13 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>1.4701137176229</v>
+        <v>31.15314491795438</v>
       </c>
       <c r="F42">
-        <v>446.6852000000001</v>
+        <v>446.6852</v>
       </c>
       <c r="G42">
-        <v>0.21</v>
+        <v>21</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -1537,16 +1537,16 @@
         <v>19</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>0.259875</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>379.2</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>20.79</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>80</v>
@@ -1566,13 +1566,13 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>2.172932294851431</v>
+        <v>25.61826681806404</v>
       </c>
       <c r="F44">
         <v>353.4128</v>
       </c>
       <c r="G44">
-        <v>2.1</v>
+        <v>14</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1589,16 +1589,16 @@
         <v>19</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0.14875</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>228.8</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>80</v>
@@ -1670,13 +1670,13 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>0.28</v>
+        <v>33.52486914515497</v>
       </c>
       <c r="F48">
         <v>493.3760000000001</v>
       </c>
       <c r="G48">
-        <v>0.28</v>
+        <v>14</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1693,16 +1693,16 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>0.1715</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>578.4978303068915</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>13.72</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>80</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>1.820000000000002</v>
+        <v>20.30922951490298</v>
       </c>
       <c r="F50">
         <v>267.8624</v>
       </c>
       <c r="G50">
-        <v>1.820000000000002</v>
+        <v>14</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1745,16 +1745,16 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>0.15225</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>12.18</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>80</v>
@@ -1774,13 +1774,13 @@
         <v>1</v>
       </c>
       <c r="E52">
-        <v>2.052104457433294</v>
+        <v>35</v>
       </c>
       <c r="F52">
         <v>350.4488000000001</v>
       </c>
       <c r="G52">
-        <v>1.75</v>
+        <v>35</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1797,16 +1797,16 @@
         <v>19</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>0.415625</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>249.6</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>33.25</v>
+        <v>0</v>
       </c>
       <c r="H53">
         <v>80</v>

--- a/MILP/model_output/master_solution_decisions.xlsx
+++ b/MILP/model_output/master_solution_decisions.xlsx
@@ -578,13 +578,13 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>22.47188389551929</v>
+        <v>0.209999999999976</v>
       </c>
       <c r="F6">
-        <v>308.7967999997442</v>
+        <v>287.2431020479866</v>
       </c>
       <c r="G6">
-        <v>21</v>
+        <v>0.209999999999976</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -601,16 +601,16 @@
         <v>19</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>0.2598750000000003</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>356.8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>20.79000000000002</v>
       </c>
       <c r="H7">
         <v>80</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>27.28394913784358</v>
+        <v>0.1399999999999579</v>
       </c>
       <c r="F8">
-        <v>387.764</v>
+        <v>362.4494294535604</v>
       </c>
       <c r="G8">
-        <v>14</v>
+        <v>0.139999999999997</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -653,16 +653,16 @@
         <v>19</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>0.1732499999999995</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>433.6</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>13.86</v>
       </c>
       <c r="H9">
         <v>80</v>
@@ -682,13 +682,13 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>26.82756624371143</v>
+        <v>0.859349996480743</v>
       </c>
       <c r="F10">
-        <v>376.7816</v>
+        <v>289.832</v>
       </c>
       <c r="G10">
-        <v>21</v>
+        <v>0.2099999999999937</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -705,16 +705,16 @@
         <v>19</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.259874999999957</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>337.6</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>20.79000000000002</v>
       </c>
       <c r="H11">
         <v>80</v>
@@ -734,13 +734,13 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="F12">
         <v>238.784</v>
       </c>
       <c r="G12">
-        <v>21</v>
+        <v>1.68</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -757,16 +757,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>0.2415</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="H13">
         <v>80</v>
@@ -890,13 +890,13 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>23.1341632769456</v>
+        <v>0.1399999999999646</v>
       </c>
       <c r="F18">
-        <v>319.2488</v>
+        <v>286.8484481991948</v>
       </c>
       <c r="G18">
-        <v>14</v>
+        <v>0.1399999999999983</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>19</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>0.1732499999999995</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>356.8</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>13.86000000000002</v>
       </c>
       <c r="H19">
         <v>80</v>
@@ -942,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>25.03523566281445</v>
+        <v>25.03523566281444</v>
       </c>
       <c r="F20">
         <v>350.5112</v>
@@ -994,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>24.24278006375409</v>
+        <v>24.2427800637541</v>
       </c>
       <c r="F22">
         <v>337.5008</v>
@@ -1046,13 +1046,13 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>29.11803213782482</v>
+        <v>0.1399999999999491</v>
       </c>
       <c r="F24">
-        <v>417.5912</v>
+        <v>383.8650001926053</v>
       </c>
       <c r="G24">
-        <v>14</v>
+        <v>0.1399999999999935</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1069,16 +1069,16 @@
         <v>19</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>0.1732499999999988</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>13.86000000000002</v>
       </c>
       <c r="H25">
         <v>80</v>
@@ -1098,13 +1098,13 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>18.55750215455832</v>
+        <v>0.715383504980014</v>
       </c>
       <c r="F26">
-        <v>242.1068</v>
+        <v>186.236</v>
       </c>
       <c r="G26">
-        <v>14</v>
+        <v>0.1399999999999992</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1121,16 +1121,16 @@
         <v>19</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>0.1732499999999997</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>13.86000000000002</v>
       </c>
       <c r="H27">
         <v>80</v>
@@ -1150,13 +1150,13 @@
         <v>1</v>
       </c>
       <c r="E28">
-        <v>21.36816696940135</v>
+        <v>0.1399999999999613</v>
       </c>
       <c r="F28">
-        <v>289.0472</v>
+        <v>227.1146568560687</v>
       </c>
       <c r="G28">
-        <v>14</v>
+        <v>0.139999999999981</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1173,16 +1173,16 @@
         <v>19</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>0.1732500000000002</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>297.6</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>13.86000000000002</v>
       </c>
       <c r="H29">
         <v>80</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0.559999999999917</v>
+        <v>0.5599999999999093</v>
       </c>
       <c r="F30">
-        <v>358.4188976461648</v>
+        <v>358.4188976461646</v>
       </c>
       <c r="G30">
-        <v>0.5599999999999739</v>
+        <v>0.5599999999999028</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1228,13 +1228,13 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0.6929999999999998</v>
+        <v>0.6930000000000012</v>
       </c>
       <c r="F31">
         <v>433.6</v>
       </c>
       <c r="G31">
-        <v>55.44000000000007</v>
+        <v>55.4400000000001</v>
       </c>
       <c r="H31">
         <v>80</v>
@@ -1358,13 +1358,13 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>33.12053028750031</v>
+        <v>0.1399999999999547</v>
       </c>
       <c r="F36">
-        <v>482.1439999999999</v>
+        <v>416.3779374891614</v>
       </c>
       <c r="G36">
-        <v>14</v>
+        <v>0.1399999999999997</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1381,16 +1381,16 @@
         <v>19</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.1732499999999992</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>491.2</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>13.86000000000001</v>
       </c>
       <c r="H37">
         <v>80</v>
@@ -1410,13 +1410,13 @@
         <v>1</v>
       </c>
       <c r="E38">
-        <v>35</v>
+        <v>0.4107609454991927</v>
       </c>
       <c r="F38">
-        <v>476.9492</v>
+        <v>366.884</v>
       </c>
       <c r="G38">
-        <v>35</v>
+        <v>0.35</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -1433,16 +1433,16 @@
         <v>19</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.4331249999999993</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>443.2</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>34.65</v>
       </c>
       <c r="H39">
         <v>80</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>26.88094398490031</v>
+        <v>0.7788180732869976</v>
       </c>
       <c r="F40">
-        <v>377.624</v>
+        <v>290.48</v>
       </c>
       <c r="G40">
-        <v>14</v>
+        <v>0.1399999999999935</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -1485,16 +1485,16 @@
         <v>19</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>0.1732499999999777</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>337.6</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>13.86000000000001</v>
       </c>
       <c r="H41">
         <v>80</v>
@@ -1514,13 +1514,13 @@
         <v>1</v>
       </c>
       <c r="E42">
-        <v>31.15314491795438</v>
+        <v>0.9903207818095969</v>
       </c>
       <c r="F42">
-        <v>446.6852</v>
+        <v>343.604</v>
       </c>
       <c r="G42">
-        <v>21</v>
+        <v>0.2099999999999937</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -1537,16 +1537,16 @@
         <v>19</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>0.2598749999999997</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>379.2</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>20.79000000000001</v>
       </c>
       <c r="H43">
         <v>80</v>
@@ -1566,13 +1566,13 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>25.61826681806404</v>
+        <v>2.0912419380986</v>
       </c>
       <c r="F44">
         <v>353.4128</v>
       </c>
       <c r="G44">
-        <v>14</v>
+        <v>1.96</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1589,16 +1589,16 @@
         <v>19</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>0.150499999999999</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>228.8</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>12.04</v>
       </c>
       <c r="H45">
         <v>80</v>
@@ -1670,13 +1670,13 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>33.52486914515497</v>
+        <v>0.28</v>
       </c>
       <c r="F48">
         <v>493.3760000000001</v>
       </c>
       <c r="G48">
-        <v>14</v>
+        <v>0.28</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1693,16 +1693,16 @@
         <v>19</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>0.1715</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>578.4978303068915</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>13.72</v>
       </c>
       <c r="H49">
         <v>80</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="E50">
-        <v>20.30922951490298</v>
+        <v>1.82</v>
       </c>
       <c r="F50">
         <v>267.8624</v>
       </c>
       <c r="G50">
-        <v>14</v>
+        <v>1.82</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1745,16 +1745,16 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>0.15225</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="H51">
         <v>80</v>
@@ -1774,13 +1774,13 @@
         <v>1</v>
       </c>
       <c r="E52">
-        <v>35</v>
+        <v>2.052104457433294</v>
       </c>
       <c r="F52">
         <v>350.4488000000001</v>
       </c>
       <c r="G52">
-        <v>35</v>
+        <v>1.75</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1797,16 +1797,16 @@
         <v>19</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>0.415625</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>249.6</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>33.25</v>
       </c>
       <c r="H53">
         <v>80</v>
@@ -1826,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="E54">
-        <v>1.744667190763831</v>
+        <v>1.744667190763824</v>
       </c>
       <c r="F54">
         <v>471.2396000000001</v>
@@ -1852,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="E55">
-        <v>0.6929999999999987</v>
+        <v>0.6929999999999925</v>
       </c>
       <c r="F55">
         <v>443.2</v>
